--- a/RC-template copy.xlsx
+++ b/RC-template copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ew-josh/Downloads/EW-Design/EW-WebView/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1363655B-3271-D242-8D7C-C8084EB5F972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4D825C-F645-B445-86DC-4137AFF5BA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="460" yWindow="1360" windowWidth="38400" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="960" windowWidth="38400" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TQL Rate Confirmation" sheetId="1" r:id="rId1"/>
@@ -50,30 +50,18 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Phone</t>
-  </si>
-  <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Fax</t>
-  </si>
-  <si>
     <t>CARRIER CONTACT</t>
   </si>
   <si>
     <t>MC/DOT#</t>
   </si>
   <si>
-    <t>Terms</t>
-  </si>
-  <si>
     <t>Address</t>
   </si>
   <si>
-    <t>Dispatcher</t>
-  </si>
-  <si>
     <t>Driver</t>
   </si>
   <si>
@@ -164,13 +152,25 @@
     <t>HOME BAY TRADING CORP</t>
   </si>
   <si>
-    <t>HB RATE CONFIRMATION FOR PO# 17337707</t>
-  </si>
-  <si>
     <t>EWLTL.COM</t>
   </si>
   <si>
     <t>HB CONTACT INFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HB RATE CONFIRMATION FOR PO# </t>
+  </si>
+  <si>
+    <t>Cell Phone 2</t>
+  </si>
+  <si>
+    <t>Cell Phone 1</t>
+  </si>
+  <si>
+    <t>HB Dispatcher Name</t>
+  </si>
+  <si>
+    <t>Carrier Dispatcher Name</t>
   </si>
 </sst>
 </file>
@@ -426,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -449,6 +449,51 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -473,26 +518,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -509,50 +548,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -796,81 +808,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
+      <c r="A1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
     </row>
     <row r="2" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="20" t="s">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
     </row>
     <row r="3" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
@@ -892,10 +904,10 @@
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
     </row>
     <row r="5" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
@@ -915,14 +927,14 @@
       <c r="O5" s="17"/>
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
     </row>
     <row r="6" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -932,76 +944,76 @@
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
     </row>
     <row r="7" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28" t="s">
+      <c r="A7" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="35"/>
     </row>
     <row r="8" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
     </row>
     <row r="9" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -1011,180 +1023,180 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
     </row>
     <row r="10" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+    </row>
+    <row r="11" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="44"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="12"/>
+    </row>
+    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+    </row>
+    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="42"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="42"/>
+    </row>
+    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="32"/>
-      <c r="R10" s="32" t="s">
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="S10" s="32"/>
-      <c r="T10" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="32"/>
-    </row>
-    <row r="11" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="12"/>
-    </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="36" t="s">
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="36"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="36"/>
-    </row>
-    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
-    </row>
-    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28"/>
-      <c r="T14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="U14" s="28"/>
+      <c r="U14" s="35"/>
     </row>
     <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="26"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="39"/>
     </row>
     <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -1194,297 +1206,297 @@
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="41"/>
+      <c r="U16" s="41"/>
     </row>
     <row r="17" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28" t="s">
+      <c r="U17" s="35"/>
+    </row>
+    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+    </row>
+    <row r="19" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28" t="s">
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="N17" s="28"/>
-      <c r="O17" s="28"/>
-      <c r="P17" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="28"/>
-      <c r="T17" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="U17" s="28"/>
-    </row>
-    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="40"/>
-      <c r="U18" s="40"/>
-    </row>
-    <row r="19" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="24"/>
     </row>
     <row r="20" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
       <c r="E20" s="32" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
       <c r="I20" s="33" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J20" s="33"/>
       <c r="K20" s="33"/>
       <c r="L20" s="32" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M20" s="32"/>
       <c r="N20" s="32"/>
       <c r="O20" s="32" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P20" s="32"/>
       <c r="Q20" s="32"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="T20" s="32"/>
       <c r="U20" s="32"/>
     </row>
     <row r="21" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="15"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="30"/>
     </row>
     <row r="22" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="38"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="38"/>
+    </row>
+    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25" t="s">
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="38"/>
+    </row>
+    <row r="24" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="39"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
+      <c r="S24" s="39"/>
+      <c r="T24" s="39"/>
+      <c r="U24" s="39"/>
+      <c r="X24" s="7"/>
+    </row>
+    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-    </row>
-    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-    </row>
-    <row r="24" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="X24" s="7"/>
-    </row>
-    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="35"/>
     </row>
     <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="26"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
+      <c r="A26" s="39"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
     </row>
     <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -1494,72 +1506,72 @@
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
       <c r="I27" s="16"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="30"/>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="30"/>
-      <c r="R27" s="30"/>
-      <c r="S27" s="30"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="30"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
     </row>
     <row r="28" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
+        <v>32</v>
+      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
       <c r="M28" s="6"/>
-      <c r="N28" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
+      <c r="N28" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="34"/>
+      <c r="T28" s="34"/>
+      <c r="U28" s="34"/>
     </row>
     <row r="29" spans="1:24" ht="115.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="24"/>
-      <c r="T29" s="24"/>
-      <c r="U29" s="24"/>
+        <v>35</v>
+      </c>
+      <c r="B29" s="36"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="37"/>
+      <c r="N29" s="37"/>
+      <c r="O29" s="37"/>
+      <c r="P29" s="37"/>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="37"/>
+      <c r="S29" s="37"/>
+      <c r="T29" s="37"/>
+      <c r="U29" s="37"/>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2533,7 +2545,26 @@
     <row r="999" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="87">
+  <mergeCells count="88">
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:L17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="J27:U27"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="A12:U12"/>
     <mergeCell ref="H14:N14"/>
     <mergeCell ref="O14:S14"/>
     <mergeCell ref="T14:U14"/>
@@ -2545,45 +2576,13 @@
     <mergeCell ref="E18:L18"/>
     <mergeCell ref="P18:S18"/>
     <mergeCell ref="J16:U16"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="G10:M10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="N10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A13:U13"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="G11:M11"/>
-    <mergeCell ref="A12:U12"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:L17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="J27:U27"/>
-    <mergeCell ref="S28:U28"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="S21:U21"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="S20:U20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="N22:U22"/>
-    <mergeCell ref="Q23:U23"/>
     <mergeCell ref="L20:N20"/>
     <mergeCell ref="B20:D20"/>
+    <mergeCell ref="Q24:U24"/>
+    <mergeCell ref="Q25:U25"/>
+    <mergeCell ref="Q26:U26"/>
+    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="L1:R1"/>
     <mergeCell ref="B29:U29"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="A23:I23"/>
@@ -2596,23 +2595,9 @@
     <mergeCell ref="J24:P24"/>
     <mergeCell ref="A24:I24"/>
     <mergeCell ref="N28:R28"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="S20:U20"/>
     <mergeCell ref="H28:L28"/>
-    <mergeCell ref="Q24:U24"/>
-    <mergeCell ref="Q25:U25"/>
-    <mergeCell ref="Q26:U26"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A4:Q5"/>
-    <mergeCell ref="A1:K3"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="L1:U1"/>
-    <mergeCell ref="L2:U2"/>
-    <mergeCell ref="L3:U3"/>
-    <mergeCell ref="R4:U5"/>
-    <mergeCell ref="J6:U6"/>
-    <mergeCell ref="R7:U7"/>
-    <mergeCell ref="R8:U8"/>
     <mergeCell ref="P19:R19"/>
     <mergeCell ref="S19:U19"/>
     <mergeCell ref="B21:D21"/>
@@ -2621,6 +2606,34 @@
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:R21"/>
     <mergeCell ref="A19:O19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="S21:U21"/>
+    <mergeCell ref="S28:U28"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="N22:U22"/>
+    <mergeCell ref="Q23:U23"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="N10:R10"/>
+    <mergeCell ref="S10:U10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:M11"/>
+    <mergeCell ref="N11:R11"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A4:Q5"/>
+    <mergeCell ref="A1:K3"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="L2:U2"/>
+    <mergeCell ref="L3:U3"/>
+    <mergeCell ref="R4:U5"/>
+    <mergeCell ref="J6:U6"/>
+    <mergeCell ref="R7:U7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/RC-template copy.xlsx
+++ b/RC-template copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ew-josh/Downloads/EW-Design/EW-WebView/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4D825C-F645-B445-86DC-4137AFF5BA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C75778-4888-C944-A927-CF54CB67F0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="960" windowWidth="38400" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TQL Rate Confirmation" sheetId="1" r:id="rId1"/>
@@ -39,16 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
-  <si>
-    <t>FIND YOUR NEXT LOAD BY VISITING</t>
-  </si>
-  <si>
-    <t>TO ENSURE PROMPT PAYMENT, SUMBMIT THIS RATE CONFIRMATION, COMPLETE BOL(S)/POD, RECEIPTS AND OTHER APPLICABLE PAPERWORK TO CINVOICES@TQL.COM. FOR OTHER OPTIONS, SEE NEXT PAGE.</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>Email</t>
   </si>
@@ -152,9 +143,6 @@
     <t>HOME BAY TRADING CORP</t>
   </si>
   <si>
-    <t>EWLTL.COM</t>
-  </si>
-  <si>
     <t>HB CONTACT INFO</t>
   </si>
   <si>
@@ -170,7 +158,22 @@
     <t>HB Dispatcher Name</t>
   </si>
   <si>
-    <t>Carrier Dispatcher Name</t>
+    <t>We will pay your company by factoring of Apex Capital, CASH WAY  RTS Financial, Bluff city, TBS OTR, TAFS, Triump, and WEX  Phoenix Capital, century finance Bluff city, TBS ,THUNDER,OTR RTS Financial,  ACH ZELLE when POD, invoice, delivery pictures, carrier collection account are ready. The quick payment requires a 3% handling fee, but monthly payment is free. Any individual collection account is not allowed.</t>
+  </si>
+  <si>
+    <t>FIND YOUR NEXT LOAD BY VISITING: EWLTL.COM</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Dispatcher Name</t>
+  </si>
+  <si>
+    <t>Cell Phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell Phone			</t>
   </si>
 </sst>
 </file>
@@ -224,13 +227,6 @@
       <i/>
       <sz val="7"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -294,6 +290,14 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -423,8 +427,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -446,128 +451,129 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -808,770 +814,772 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+    </row>
+    <row r="2" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+    </row>
+    <row r="3" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+    </row>
+    <row r="4" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
+    </row>
+    <row r="5" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="44"/>
+      <c r="T5" s="44"/>
+      <c r="U5" s="44"/>
+    </row>
+    <row r="6" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+    </row>
+    <row r="7" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-    </row>
-    <row r="2" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="19" t="s">
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="19"/>
-      <c r="T2" s="19"/>
-      <c r="U2" s="19"/>
-    </row>
-    <row r="3" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="20" t="s">
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+    </row>
+    <row r="8" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="45"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+    </row>
+    <row r="9" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+    </row>
+    <row r="10" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-    </row>
-    <row r="4" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-    </row>
-    <row r="5" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-    </row>
-    <row r="6" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-    </row>
-    <row r="7" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="35" t="s">
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37"/>
+    </row>
+    <row r="11" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="41"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="41"/>
+      <c r="U11" s="42"/>
+    </row>
+    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="18"/>
+    </row>
+    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+    </row>
+    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="35"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="35"/>
-    </row>
-    <row r="8" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18"/>
-    </row>
-    <row r="9" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="s">
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="45"/>
-      <c r="U9" s="45"/>
-    </row>
-    <row r="10" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-    </row>
-    <row r="11" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="44"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="12"/>
-    </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="43" t="s">
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-    </row>
-    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
-      <c r="U13" s="42"/>
-    </row>
-    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35" t="s">
+      <c r="U14" s="10"/>
+    </row>
+    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+    </row>
+    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+    </row>
+    <row r="17" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U14" s="35"/>
-    </row>
-    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="39"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="39"/>
-      <c r="U15" s="39"/>
-    </row>
-    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16" t="s">
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-    </row>
-    <row r="17" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="35" t="s">
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35" t="s">
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35" t="s">
+      <c r="U17" s="10"/>
+    </row>
+    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+    </row>
+    <row r="19" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35" t="s">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="U17" s="35"/>
-    </row>
-    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="39"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="39"/>
-      <c r="S18" s="39"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="46"/>
-    </row>
-    <row r="19" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
     </row>
     <row r="20" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32" t="s">
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="33" t="s">
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="32"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="T20" s="32"/>
-      <c r="U20" s="32"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
     </row>
     <row r="21" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="30"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="30"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="33"/>
     </row>
     <row r="22" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+    </row>
+    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38" t="s">
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-      <c r="R22" s="38"/>
-      <c r="S22" s="38"/>
-      <c r="T22" s="38"/>
-      <c r="U22" s="38"/>
-    </row>
-    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="38" t="s">
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+    </row>
+    <row r="24" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="X24" s="7"/>
+    </row>
+    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+    </row>
+    <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+    </row>
+    <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="R23" s="38"/>
-      <c r="S23" s="38"/>
-      <c r="T23" s="38"/>
-      <c r="U23" s="38"/>
-    </row>
-    <row r="24" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="39"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
-      <c r="S24" s="39"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="39"/>
-      <c r="X24" s="7"/>
-    </row>
-    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="35"/>
-    </row>
-    <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="39"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="39"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="39"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="39"/>
-      <c r="R26" s="39"/>
-      <c r="S26" s="39"/>
-      <c r="T26" s="39"/>
-      <c r="U26" s="39"/>
-    </row>
-    <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="41"/>
-      <c r="S27" s="41"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="41"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="16"/>
     </row>
     <row r="28" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
+        <v>29</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
       <c r="M28" s="6"/>
-      <c r="N28" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="34"/>
+      <c r="N28" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="36"/>
     </row>
     <row r="29" spans="1:24" ht="115.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="36"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="37"/>
-      <c r="P29" s="37"/>
-      <c r="Q29" s="37"/>
-      <c r="R29" s="37"/>
-      <c r="S29" s="37"/>
-      <c r="T29" s="37"/>
-      <c r="U29" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22"/>
+      <c r="U29" s="22"/>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2545,43 +2553,51 @@
     <row r="999" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="88">
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:L17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="J9:R9"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="J27:U27"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A13:U13"/>
-    <mergeCell ref="A12:U12"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:S14"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O15:S15"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:L18"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="J16:U16"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="Q24:U24"/>
-    <mergeCell ref="Q25:U25"/>
-    <mergeCell ref="Q26:U26"/>
-    <mergeCell ref="R8:U8"/>
+  <mergeCells count="90">
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="L2:U2"/>
+    <mergeCell ref="J6:U6"/>
+    <mergeCell ref="R7:U7"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="A3:U5"/>
+    <mergeCell ref="S28:U28"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="N22:U22"/>
+    <mergeCell ref="Q23:U23"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="N10:R10"/>
+    <mergeCell ref="S10:U10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:M11"/>
+    <mergeCell ref="N11:R11"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="S19:U19"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="S21:U21"/>
     <mergeCell ref="L1:R1"/>
     <mergeCell ref="B29:U29"/>
     <mergeCell ref="J23:P23"/>
@@ -2598,42 +2614,36 @@
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="S20:U20"/>
     <mergeCell ref="H28:L28"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="S19:U19"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="S21:U21"/>
-    <mergeCell ref="S28:U28"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="N22:U22"/>
-    <mergeCell ref="Q23:U23"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="I10:M10"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="N10:R10"/>
-    <mergeCell ref="S10:U10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="I11:M11"/>
-    <mergeCell ref="N11:R11"/>
-    <mergeCell ref="S11:U11"/>
-    <mergeCell ref="S1:U1"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A4:Q5"/>
-    <mergeCell ref="A1:K3"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="L2:U2"/>
-    <mergeCell ref="L3:U3"/>
-    <mergeCell ref="R4:U5"/>
-    <mergeCell ref="J6:U6"/>
-    <mergeCell ref="R7:U7"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="Q24:U24"/>
+    <mergeCell ref="Q25:U25"/>
+    <mergeCell ref="Q26:U26"/>
+    <mergeCell ref="J27:U27"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="O14:S14"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="O15:S15"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="J16:U16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="J9:R9"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="A18:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
